--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0004.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-1-finland-as-a-part-of-sweden-and-russia__0004.xlsx
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Bara adeln</t>
+          <t>Män med egendom</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Bara präster</t>
+          <t>Borgare och jordägare</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Bara officerare</t>
+          <t>Stadsbor med hög inkomst</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Finland var sist i Europa</t>
+          <t>Finland var bland de sista i Norden</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Finland gav aldrig rösträtt till kvinnor</t>
+          <t>Finland införde det på 1920-talet</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Finland gav rösträtt först efter 2000</t>
+          <t>Finland införde det först efter 1945</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Finland var 50:e landet i världen</t>
+          <t>Finland var femte landet i världen</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Finland var första landet i Afrika</t>
+          <t>Finland var tionde landet i världen</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Finland var andra landet i Asien</t>
+          <t>Finland var 20:e landet i världen</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Rätt att bli kung</t>
+          <t>Rätt att rösta i riksdagsval</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Rätt att slippa skatt</t>
+          <t>Rätt att bli minister</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Rätt att stoppa val</t>
+          <t>Rätt att vara jurymedlem</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>De var de första kvinnliga presidenterna</t>
+          <t>De var de första kvinnliga ministrarna i Finland</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>De var de första kvinnliga generalerna</t>
+          <t>De var de första kvinnliga statsministrarna i Norden</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>De var de första kvinnliga prästerna</t>
+          <t>De var de första kvinnliga biskoparna i Finland</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>En ny union med Sverige bildades</t>
+          <t>En koalitionsregering bildades</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Finland blev koloni igen</t>
+          <t>En ny grundlag antogs</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Alla partier förbjöds</t>
+          <t>Konflikter om makten fördjupades</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>För mycket överskott av mat</t>
+          <t>Oenighet om makten efter 1917</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Att ingen ville rösta</t>
+          <t>Radikalisering i både höger och vänster</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Att Finland hade tropiskt klimat</t>
+          <t>Konflikter om arbetsvillkor och löner</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Brist på språk i landet</t>
+          <t>Religiösa motsättningar</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>För många järnvägar</t>
+          <t>Etniska motsättningar</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>För få skolor</t>
+          <t>Territoriell konflikt med Sverige</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>NATO och EU</t>
+          <t>Röda armén och Vita armén</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Sverige och Norge</t>
+          <t>Monarkister och republikaner</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Öst och Västtyskland</t>
+          <t>Socialdemokrater och konservativa</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Kungafamiljen</t>
+          <t>Industrimagnater och godsägare</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Endast präster</t>
+          <t>Högre tjänstemän och officerare</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Endast jurister</t>
+          <t>Borgerskap i stora städer</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Bara fabriksarbetare</t>
+          <t>Arbetare i industristäder</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Endast sjömän</t>
+          <t>Torpare och statare</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Endast studenter</t>
+          <t>Sjömän och hamnarbetare</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Båda exakt lika</t>
+          <t>Båda hade liknande resurser</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Ingen sida</t>
+          <t>Det varierade mellan olika områden</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>I december 1918</t>
+          <t>I mars 1918</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>I januari 1919</t>
+          <t>I maj 1918</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>I maj 1917</t>
+          <t>I september 1918</t>
         </is>
       </c>
       <c r="G28" s="14" t="n">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>Ingen vann</t>
+          <t>Det blev ett oavgjort resultat</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>3 700</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>370 000</t>
+          <t>50 000</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>3 700 000</t>
+          <t>100 000</t>
         </is>
       </c>
       <c r="G30" s="14" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>Båda lika många</t>
+          <t>Civila utan koppling till någon sida</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>Ingen sida</t>
+          <t>Båda sidor ungefär lika många</t>
         </is>
       </c>
       <c r="G31" s="14" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Överflöd och rikedom</t>
+          <t>Maktvakuum efter ryska revolutionen</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>Brist på skog</t>
+          <t>Strid om jordreformer</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>För många universitet</t>
+          <t>Konflikter om arbetsvillkor</t>
         </is>
       </c>
       <c r="G32" s="14" t="n">
